--- a/config/example_config.xlsx
+++ b/config/example_config.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_drive_BACKUP\Code\MyProject\club_file_system\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C9EE74-D5B2-4657-837B-415CDDE4E365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB03BC23-2168-4940-A1CA-43319F9CC46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{87A57A4E-B348-417B-A354-DEEE58466050}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="2" xr2:uid="{87A57A4E-B348-417B-A354-DEEE58466050}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="主分類" sheetId="1" r:id="rId1"/>
+    <sheet name="細分類" sheetId="2" r:id="rId2"/>
+    <sheet name="活動代碼" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -25,54 +27,142 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t>主分類名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動相關</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>評鑑資料</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>行政管理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>財務</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>幹部管理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>G</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>主分類代碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>細分類名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>企劃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>照片</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>報帳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>會議記錄</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>成果報告</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>細分類代碼</t>
-  </si>
-  <si>
-    <t>活動名稱</t>
-  </si>
-  <si>
-    <t>活動代碼</t>
-  </si>
-  <si>
-    <t>活動相關</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>企劃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>PL</t>
-  </si>
-  <si>
-    <t>哈盆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈盆古道</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>仙湖野營</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>福源山淨山</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>南澳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>校園路跑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HP</t>
-  </si>
-  <si>
-    <t>照片</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>仙湖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>FL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FYS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RUN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -451,67 +541,203 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDF12791-FC34-4AE2-BA52-E629D1766F38}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB69075-5E5F-4EDA-8BCF-249C57FE74CB}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5B1FE8-E72F-41BD-A980-9F35FEFC728D}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
